--- a/RESPONSÁVEIS POR BASES .xlsx
+++ b/RESPONSÁVEIS POR BASES .xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jet Express\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jet Express\Desktop\SLA - CELULAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA621DF8-E2C4-4992-A044-EED668DB8459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8798FC2-AF06-498F-9AC9-FB247EB073D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{814D9627-4A8B-4491-BF47-57A5D2033E0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -409,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -435,6 +435,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -769,16 +771,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC22AD61-64EC-4D13-BFE4-30A2217AEED5}">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="17.399999999999999">
+    <row r="1" spans="1:14" ht="17.399999999999999">
       <c r="A1" s="1" t="s">
         <v>89</v>
       </c>
@@ -792,7 +797,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -805,8 +810,10 @@
       <c r="D2" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="G2" s="7"/>
+      <c r="N2" s="9"/>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -819,8 +826,10 @@
       <c r="D3" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="G3" s="7"/>
+      <c r="N3" s="9"/>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -833,8 +842,10 @@
       <c r="D4" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="G4" s="7"/>
+      <c r="N4" s="9"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -847,8 +858,10 @@
       <c r="D5" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="G5" s="7"/>
+      <c r="N5" s="9"/>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -861,8 +874,10 @@
       <c r="D6" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="G6" s="5"/>
+      <c r="N6" s="9"/>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -875,8 +890,9 @@
       <c r="D7" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="N7" s="9"/>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
@@ -889,8 +905,9 @@
       <c r="D8" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="N8" s="9"/>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -903,8 +920,9 @@
       <c r="D9" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="N9" s="9"/>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -917,8 +935,9 @@
       <c r="D10" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="N10" s="9"/>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -931,8 +950,9 @@
       <c r="D11" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="N11" s="9"/>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -945,8 +965,9 @@
       <c r="D12" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="N12" s="9"/>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -959,8 +980,9 @@
       <c r="D13" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="N13" s="9"/>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
@@ -973,8 +995,9 @@
       <c r="D14" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="N14" s="9"/>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -987,8 +1010,9 @@
       <c r="D15" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="N15" s="9"/>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -1001,8 +1025,9 @@
       <c r="D16" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="N16" s="9"/>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
@@ -1015,8 +1040,9 @@
       <c r="D17" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="N17" s="9"/>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="2" t="s">
         <v>23</v>
       </c>
@@ -1029,8 +1055,9 @@
       <c r="D18" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="N18" s="9"/>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="2" t="s">
         <v>24</v>
       </c>
@@ -1043,8 +1070,9 @@
       <c r="D19" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="N19" s="9"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="2" t="s">
         <v>25</v>
       </c>
@@ -1057,8 +1085,9 @@
       <c r="D20" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="N20" s="9"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
@@ -1071,8 +1100,9 @@
       <c r="D21" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="N21" s="9"/>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
@@ -1085,8 +1115,9 @@
       <c r="D22" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="N22" s="9"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="2" t="s">
         <v>28</v>
       </c>
@@ -1099,8 +1130,9 @@
       <c r="D23" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="N23" s="9"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="2" t="s">
         <v>29</v>
       </c>
@@ -1113,8 +1145,9 @@
       <c r="D24" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="N24" s="9"/>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
@@ -1127,8 +1160,9 @@
       <c r="D25" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="N25" s="9"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="2" t="s">
         <v>31</v>
       </c>
@@ -1141,8 +1175,9 @@
       <c r="D26" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
+      <c r="N26" s="9"/>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -1155,8 +1190,9 @@
       <c r="D27" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="N27" s="9"/>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="2" t="s">
         <v>33</v>
       </c>
@@ -1169,8 +1205,9 @@
       <c r="D28" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="N28" s="9"/>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="2" t="s">
         <v>34</v>
       </c>
@@ -1183,8 +1220,9 @@
       <c r="D29" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="N29" s="9"/>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="2" t="s">
         <v>35</v>
       </c>
@@ -1197,8 +1235,9 @@
       <c r="D30" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="N30" s="9"/>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="2" t="s">
         <v>36</v>
       </c>
@@ -1211,8 +1250,9 @@
       <c r="D31" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="N31" s="9"/>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="2" t="s">
         <v>37</v>
       </c>
@@ -1225,8 +1265,9 @@
       <c r="D32" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="N32" s="9"/>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="2" t="s">
         <v>38</v>
       </c>
@@ -1239,8 +1280,9 @@
       <c r="D33" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="N33" s="9"/>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="2" t="s">
         <v>39</v>
       </c>
@@ -1253,8 +1295,9 @@
       <c r="D34" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
+      <c r="N34" s="9"/>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="2" t="s">
         <v>40</v>
       </c>
@@ -1267,8 +1310,9 @@
       <c r="D35" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="N35" s="9"/>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="2" t="s">
         <v>41</v>
       </c>
@@ -1281,8 +1325,9 @@
       <c r="D36" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="N36" s="9"/>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="2" t="s">
         <v>42</v>
       </c>
@@ -1295,8 +1340,9 @@
       <c r="D37" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="N37" s="9"/>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="2" t="s">
         <v>43</v>
       </c>
@@ -1309,8 +1355,9 @@
       <c r="D38" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="N38" s="9"/>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="2" t="s">
         <v>44</v>
       </c>
@@ -1323,8 +1370,9 @@
       <c r="D39" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="N39" s="9"/>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="2" t="s">
         <v>45</v>
       </c>
@@ -1337,8 +1385,9 @@
       <c r="D40" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="N40" s="9"/>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="2" t="s">
         <v>46</v>
       </c>
@@ -1351,8 +1400,9 @@
       <c r="D41" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="N41" s="9"/>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="2" t="s">
         <v>47</v>
       </c>
@@ -1365,8 +1415,9 @@
       <c r="D42" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="N42" s="9"/>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="2" t="s">
         <v>48</v>
       </c>
@@ -1379,8 +1430,9 @@
       <c r="D43" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="N43" s="9"/>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="2" t="s">
         <v>49</v>
       </c>
@@ -1393,8 +1445,9 @@
       <c r="D44" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="N44" s="9"/>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" s="4" t="s">
         <v>50</v>
       </c>
@@ -1407,8 +1460,9 @@
       <c r="D45" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:4">
+      <c r="N45" s="9"/>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" s="5" t="s">
         <v>51</v>
       </c>
@@ -1421,8 +1475,9 @@
       <c r="D46" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="N46" s="9"/>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" s="6" t="s">
         <v>52</v>
       </c>
@@ -1435,6 +1490,100 @@
       <c r="D47" s="7" t="s">
         <v>3</v>
       </c>
+      <c r="N47" s="9"/>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="N48" s="9"/>
+    </row>
+    <row r="49" spans="14:14">
+      <c r="N49" s="9"/>
+    </row>
+    <row r="50" spans="14:14">
+      <c r="N50" s="9"/>
+    </row>
+    <row r="51" spans="14:14">
+      <c r="N51" s="9"/>
+    </row>
+    <row r="52" spans="14:14">
+      <c r="N52" s="9"/>
+    </row>
+    <row r="53" spans="14:14">
+      <c r="N53" s="9"/>
+    </row>
+    <row r="54" spans="14:14">
+      <c r="N54" s="9"/>
+    </row>
+    <row r="55" spans="14:14">
+      <c r="N55" s="9"/>
+    </row>
+    <row r="56" spans="14:14">
+      <c r="N56" s="9"/>
+    </row>
+    <row r="57" spans="14:14">
+      <c r="N57" s="9"/>
+    </row>
+    <row r="58" spans="14:14">
+      <c r="N58" s="9"/>
+    </row>
+    <row r="59" spans="14:14">
+      <c r="N59" s="9"/>
+    </row>
+    <row r="60" spans="14:14">
+      <c r="N60" s="9"/>
+    </row>
+    <row r="61" spans="14:14">
+      <c r="N61" s="9"/>
+    </row>
+    <row r="62" spans="14:14">
+      <c r="N62" s="9"/>
+    </row>
+    <row r="63" spans="14:14">
+      <c r="N63" s="9"/>
+    </row>
+    <row r="64" spans="14:14">
+      <c r="N64" s="9"/>
+    </row>
+    <row r="65" spans="14:14">
+      <c r="N65" s="9"/>
+    </row>
+    <row r="66" spans="14:14">
+      <c r="N66" s="9"/>
+    </row>
+    <row r="67" spans="14:14">
+      <c r="N67" s="9"/>
+    </row>
+    <row r="68" spans="14:14">
+      <c r="N68" s="9"/>
+    </row>
+    <row r="69" spans="14:14">
+      <c r="N69" s="9"/>
+    </row>
+    <row r="70" spans="14:14">
+      <c r="N70" s="9"/>
+    </row>
+    <row r="71" spans="14:14">
+      <c r="N71" s="9"/>
+    </row>
+    <row r="72" spans="14:14">
+      <c r="N72" s="9"/>
+    </row>
+    <row r="73" spans="14:14">
+      <c r="N73" s="9"/>
+    </row>
+    <row r="74" spans="14:14">
+      <c r="N74" s="9"/>
+    </row>
+    <row r="75" spans="14:14">
+      <c r="N75" s="9"/>
+    </row>
+    <row r="76" spans="14:14">
+      <c r="N76" s="9"/>
+    </row>
+    <row r="77" spans="14:14">
+      <c r="N77" s="9"/>
+    </row>
+    <row r="78" spans="14:14">
+      <c r="N78" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
